--- a/Result/checksun_type/基礎工程.xlsx
+++ b/Result/checksun_type/基礎工程.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>28.73</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>28.76</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>28.83</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>28.83</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>201.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>221.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>221.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>379.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>362.54</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>362.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-26.67944066689364</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>201</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>201.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>28.72</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>28.76</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>28.84</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>28.84</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>107.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>279.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>279.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>379.1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>366.02</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>366.02</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-17.95352730265512</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>107</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>28.68</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>28.76</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>28.85</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>28.85</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>427.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>581.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>581</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>371.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>371.3</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>371.3</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>5.224689192780431</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>427</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>427.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>28.69</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>28.76</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>28.86</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>28.86</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>310.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>592.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>592</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>352.5</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>376.6</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>376.6</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>3.864116715088983</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>310</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>310.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>28.75</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>28.73</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>28.86</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>28.86</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>64.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>542.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>542.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>324.4</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>374.96</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>374.96</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>14.31815186427667</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>64</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>64.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>28.68</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>28.69</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>28.86</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>28.86</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>491.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>536.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>536.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>342.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>386.84</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>386.84</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>55.09826808224915</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>491</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>491.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>28.73</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>28.69</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>28.88</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>28.88</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>1613.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>478.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>478.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>293.4</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>397.82</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>397.82</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>65.63778167641522</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>1613</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>1613.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>28.87</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>28.72</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>28.89</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>28.89</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>482.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>162.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>162.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>240.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>387.16</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>387.16</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-41.86426253464813</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>482</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>482.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>28.88</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>28.74</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>28.9</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>28.74</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>28.9</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>64.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>113</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>232.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>392.66</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>392.66</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-72.76488774564399</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>64</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>64.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>28.82</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>28.72</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>28.9</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>28.9</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>32.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>106</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>300.4</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>392.32</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>392.32</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-69.5241777704365</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>32</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>28.91</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>28.74</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>28.91</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>28.74</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>28.91</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>201.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>148.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>148.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>381.8</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>398.26</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>398.26</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-58.98301431405304</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>201</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>201.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>165.6</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>163.02</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>160.83</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>163.02</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>160.83</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>74566654.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>58486136.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>58486136.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>58606873.6</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>70642832.02</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>70642832.02</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-1307560.096186429</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>74566654</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>74566654.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>163.7</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>162.93</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>160.46</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>162.93</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>160.46</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>42057189.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>51280880.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>51280880.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>57575110.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>70368392.78</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>70368392.78</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-2977612.849109128</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>42057189</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>42057189.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>162.4</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>163.1</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>160.23</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>163.1</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>160.23</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>86690785.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>57113679.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>57113679.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>64547068.7</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>70595791.64</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>70595791.64</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-1773902.21581623</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>86690785</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>86690785.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>161.6</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>163.32</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>160.05</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>163.32</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>160.05</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>60623888.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>52450873.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>52450873.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>60032236.0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>69475167.82</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>69475167.81999999</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-4773132.94626151</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>60623888</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>60623888.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>160.4</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>163.85</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>159.88</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>163.85</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>159.88</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>28492168.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>47694181.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>47694181</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>56493562.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>68696315.04</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>68696315.04000001</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-6094397.420245431</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>28492168</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>28492168.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>159.4</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>164.42</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>159.69</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>164.42</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>159.69</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>38540371.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>58727610.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>58727610.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>57494793.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>69451049.8</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>69451049.8</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-4321576.760927983</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>38540371</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>38540371.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>159.0</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>164.95</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>159.6</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>164.95</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>159.6</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>71221184.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>63869339.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>63869339.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>58008720.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>70188106.76</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>70188106.76000001</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-2711226.970441341</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>71221184</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>71221184.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>158.9</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>165.38</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>159.41</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>165.38</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>159.41</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>63376756.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>71980458.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>71980458.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>59415753.1</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>69152957.06</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>69152957.06</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-3815413.413658947</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>63376756</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>63376756.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>159.3</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>165.7</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>159.21</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>165.7</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>159.21</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>36840426.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>67613598.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>67613598.59999999</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>63171366.2</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>68561486.4</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>68561486.40000001</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-4416083.42491056</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>36840426</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>36840426.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>160.8</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>166.2</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>159.08</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>166.2</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>159.08</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>83659315.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>65292944.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>65292944.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>63664049.4</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>69466030.4</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>69466030.40000001</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-2273287.961523205</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>83659315</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>83659315.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>162.4</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>166.95</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>158.97</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>166.95</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>158.97</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>64249018.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>56261977.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>56261977.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>58685909.5</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>68228488.76</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>68228488.76000001</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-4147272.265201129</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>64249018</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>64249018.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>37.47</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>38.08</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>40.03</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>40.03</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>35810040.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>75499582.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>75499582.59999999</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>55792550.2</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>33454972.78</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>33454972.78</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>7886638.29228013</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>35810040</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>35810040.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>36.87</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>38.11</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>40.07</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>40.07</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>39561838.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>77102277.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>77102277.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>54515793.2</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>33864219.92</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>33864219.92</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>11730479.54280426</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>39561838</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>39561838.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>36.60000000000001</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>38.22</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>40.17</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>40.17</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>232650449.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>74142370.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>74142370</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>57245793.0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>34130931.06</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>34130931.06</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>16400757.27416717</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>232650449</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>36.61</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>40.3</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>41298962.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>35487232.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>35487232</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>35914543.8</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>29950115.64</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>29950115.64</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>1798775.809179619</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>41298962</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>41298962.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>36.73</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>40.43</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>40.43</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>28176624.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>37871124.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>37871124</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>34509118.0</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>29545425.32</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>29545425.32</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>1376505.330298137</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>28176624</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>28176624.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>37.07000000000001</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>40.58</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>40.58</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>43823516.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>36085517.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>36085517.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>35025550.9</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>29409986.0</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>29409986</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>2130065.670099653</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>43823516</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>43823516.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>37.47000000000001</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>39.02</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>40.75</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>40.75</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>24762299.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>31929308.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>31929308.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>32595150.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>29130934.74</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>29130934.74</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>1454053.953026839</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>24762299</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>24762299.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>37.65000000000001</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>39.23</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>40.9</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>40.9</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>39374759.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>40349216.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>40349216</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>31454761.9</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>29061426.18</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>29061426.18</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>2478665.680314712</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>39374759</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>39374759.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>37.99</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>39.42</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>41.05</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>41.05</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>53218422.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>36341855.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>36341855.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>29562657.9</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>28846965.04</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>28846965.04</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>2288252.230714723</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>53218422</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>53218422.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>38.31</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>39.58</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>41.17</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>41.17</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>19248593.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>31147112.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>31147112</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>25871081.1</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>28091032.78</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>28091032.78</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>451260.1159035005</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>19248593</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>19248593.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>38.46</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>39.69</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>41.29</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>41.29</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>23042470.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>33965584.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>33965584</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>26178217.9</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>28206383.42</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>28206383.42</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>1450493.769176625</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>23042470</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>23042470.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/基礎工程.xlsx
+++ b/Result/checksun_type/基礎工程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ23"/>
+  <dimension ref="A1:CJ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10149,6 +10149,4648 @@
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-1.55</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>325.91</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>38.25</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-28.68</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2025-08-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>43.15</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>-11.36</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>-15.62</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>57.58</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>-3.89</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>-3.53</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>38.74</t>
+        </is>
+      </c>
+      <c r="AM24" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>39.48</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>40.93</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>59.95</t>
+        </is>
+      </c>
+      <c r="AQ24" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>-113.14</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>148998047.268034</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>12502974.0</t>
+        </is>
+      </c>
+      <c r="AX24" t="n">
+        <v>14661037.6</v>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>20557419.7</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>32207875.34</v>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>-5896382</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>-1246342.232336838</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>-5563232.276525833</t>
+        </is>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>12502974.0</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>-7.83</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK24" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN24" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO24" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP24" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ24" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS24" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="BT24" t="inlineStr">
+        <is>
+          <t>6.54</t>
+        </is>
+      </c>
+      <c r="BU24" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV24" t="inlineStr">
+        <is>
+          <t>15.81</t>
+        </is>
+      </c>
+      <c r="BW24" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX24" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY24" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ24" t="inlineStr">
+        <is>
+          <t>12284</t>
+        </is>
+      </c>
+      <c r="CA24" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC24" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD24" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="CE24" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="CF24" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CG24" t="inlineStr">
+        <is>
+          <t>38.25</t>
+        </is>
+      </c>
+      <c r="CH24" t="inlineStr">
+        <is>
+          <t>36.35</t>
+        </is>
+      </c>
+      <c r="CI24" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
+        </is>
+      </c>
+      <c r="CJ24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>410.32</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>38.85</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-63.08</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2025-08-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>43.15</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>-9.97</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>-15.62</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>4.37</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>84.98</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>-4.03</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>-3.47</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>38.85</t>
+        </is>
+      </c>
+      <c r="AM25" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>39.56</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>40.98</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>68.34</t>
+        </is>
+      </c>
+      <c r="AQ25" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>-115.10</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>148998047.268034</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>15869530.0</t>
+        </is>
+      </c>
+      <c r="AX25" t="n">
+        <v>15717891.6</v>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>42572167.2</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>32421504.8</v>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>-26854275</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>-461453.1333933839</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>-5227155.702291623</t>
+        </is>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>15869530.0</t>
+        </is>
+      </c>
+      <c r="BE25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>-6.39</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK25" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN25" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO25" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP25" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ25" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS25" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="BT25" t="inlineStr">
+        <is>
+          <t>6.54</t>
+        </is>
+      </c>
+      <c r="BU25" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV25" t="inlineStr">
+        <is>
+          <t>15.81</t>
+        </is>
+      </c>
+      <c r="BW25" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX25" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY25" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ25" t="inlineStr">
+        <is>
+          <t>12284</t>
+        </is>
+      </c>
+      <c r="CA25" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC25" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD25" t="inlineStr">
+        <is>
+          <t>39.05</t>
+        </is>
+      </c>
+      <c r="CE25" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="CF25" t="inlineStr">
+        <is>
+          <t>38.55</t>
+        </is>
+      </c>
+      <c r="CG25" t="inlineStr">
+        <is>
+          <t>38.85</t>
+        </is>
+      </c>
+      <c r="CH25" t="inlineStr">
+        <is>
+          <t>36.35</t>
+        </is>
+      </c>
+      <c r="CI25" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
+        </is>
+      </c>
+      <c r="CJ25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>435.235</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>39.05</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-63.70</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2025-08-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>43.15</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>-9.50</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>-15.62</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>97.73</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>90.23</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>-4.17</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>-3.40</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="AM26" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>41.03</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>63.94</t>
+        </is>
+      </c>
+      <c r="AQ26" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>-117.68</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>148998047.268034</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>16996914.0</t>
+        </is>
+      </c>
+      <c r="AX26" t="n">
+        <v>16375301.2</v>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>45115110.4</t>
+        </is>
+      </c>
+      <c r="AZ26" t="n">
+        <v>32578634.98</v>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>-28739809</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>405038.2427699324</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>-4921064.606875196</t>
+        </is>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>16996914.0</t>
+        </is>
+      </c>
+      <c r="BE26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF26" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG26" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>-5.90</t>
+        </is>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ26" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK26" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL26" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN26" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO26" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP26" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ26" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS26" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="BT26" t="inlineStr">
+        <is>
+          <t>6.54</t>
+        </is>
+      </c>
+      <c r="BU26" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV26" t="inlineStr">
+        <is>
+          <t>15.81</t>
+        </is>
+      </c>
+      <c r="BW26" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX26" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY26" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ26" t="inlineStr">
+        <is>
+          <t>12284</t>
+        </is>
+      </c>
+      <c r="CA26" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC26" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD26" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="CE26" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="CF26" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="CG26" t="inlineStr">
+        <is>
+          <t>39.05</t>
+        </is>
+      </c>
+      <c r="CH26" t="inlineStr">
+        <is>
+          <t>36.35</t>
+        </is>
+      </c>
+      <c r="CI26" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
+        </is>
+      </c>
+      <c r="CJ26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>358.496</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-1.18</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-63.30</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2025-08-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>43.15</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>-10.31</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>-15.62</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>82.22</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>87.65</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>-4.37</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>-3.34</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>38.87</t>
+        </is>
+      </c>
+      <c r="AM27" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>41.08</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>55.74</t>
+        </is>
+      </c>
+      <c r="AQ27" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>-120.51</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>148998047.268034</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>13860324.0</t>
+        </is>
+      </c>
+      <c r="AX27" t="n">
+        <v>16966580.2</v>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>46233081.4</t>
+        </is>
+      </c>
+      <c r="AZ27" t="n">
+        <v>32635911.38</v>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>-29266501</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>1373420.579069047</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>-4428830.448891897</t>
+        </is>
+      </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>13860324.0</t>
+        </is>
+      </c>
+      <c r="BE27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF27" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG27" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>-6.75</t>
+        </is>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ27" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK27" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL27" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN27" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO27" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP27" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ27" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS27" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="BT27" t="inlineStr">
+        <is>
+          <t>6.54</t>
+        </is>
+      </c>
+      <c r="BU27" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV27" t="inlineStr">
+        <is>
+          <t>15.81</t>
+        </is>
+      </c>
+      <c r="BW27" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX27" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY27" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ27" t="inlineStr">
+        <is>
+          <t>12284</t>
+        </is>
+      </c>
+      <c r="CA27" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC27" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD27" t="inlineStr">
+        <is>
+          <t>39.05</t>
+        </is>
+      </c>
+      <c r="CE27" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="CF27" t="inlineStr">
+        <is>
+          <t>38.45</t>
+        </is>
+      </c>
+      <c r="CG27" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="CH27" t="inlineStr">
+        <is>
+          <t>36.35</t>
+        </is>
+      </c>
+      <c r="CI27" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
+        </is>
+      </c>
+      <c r="CJ27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>363.213</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>38.85</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-56.62</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2025-08-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>43.15</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>-9.97</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>-15.62</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>90.74</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>91.36</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>-4.56</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>-3.22</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>38.95</t>
+        </is>
+      </c>
+      <c r="AM28" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>41.11</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>52.64</t>
+        </is>
+      </c>
+      <c r="AQ28" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>-123.37</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>148998047.268034</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>14075446.0</t>
+        </is>
+      </c>
+      <c r="AX28" t="n">
+        <v>21356523.4</v>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>49229400.6</t>
+        </is>
+      </c>
+      <c r="AZ28" t="n">
+        <v>32854915.68</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>-27872877</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>2428375.311425582</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>-3231403.064312473</t>
+        </is>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>14075446.0</t>
+        </is>
+      </c>
+      <c r="BE28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF28" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG28" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>-6.39</t>
+        </is>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ28" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK28" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL28" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM28" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN28" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO28" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP28" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ28" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR28" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS28" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="BT28" t="inlineStr">
+        <is>
+          <t>6.54</t>
+        </is>
+      </c>
+      <c r="BU28" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV28" t="inlineStr">
+        <is>
+          <t>15.81</t>
+        </is>
+      </c>
+      <c r="BW28" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX28" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY28" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ28" t="inlineStr">
+        <is>
+          <t>12284</t>
+        </is>
+      </c>
+      <c r="CA28" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC28" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD28" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="CE28" t="inlineStr">
+        <is>
+          <t>38.95</t>
+        </is>
+      </c>
+      <c r="CF28" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="CG28" t="inlineStr">
+        <is>
+          <t>38.85</t>
+        </is>
+      </c>
+      <c r="CH28" t="inlineStr">
+        <is>
+          <t>36.35</t>
+        </is>
+      </c>
+      <c r="CI28" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
+        </is>
+      </c>
+      <c r="CJ28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>455.261</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-1.44</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-47.41</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2025-08-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>43.15</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>-10.08</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>-15.62</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>94.44</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>-4.72</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>-3.16</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="AM29" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>39.86</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>41.16</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>47.01</t>
+        </is>
+      </c>
+      <c r="AQ29" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>-126.44</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>148998047.268034</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>17787244.0</t>
+        </is>
+      </c>
+      <c r="AX29" t="n">
+        <v>26453801.8</v>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>50298085.9</t>
+        </is>
+      </c>
+      <c r="AZ29" t="n">
+        <v>33264214.78</v>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>-23844284</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>3457425.925196137</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>-1428434.048330702</t>
+        </is>
+      </c>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>17787244.0</t>
+        </is>
+      </c>
+      <c r="BE29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF29" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG29" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>-6.51</t>
+        </is>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ29" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK29" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL29" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM29" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN29" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO29" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP29" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ29" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR29" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS29" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="BT29" t="inlineStr">
+        <is>
+          <t>6.54</t>
+        </is>
+      </c>
+      <c r="BU29" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV29" t="inlineStr">
+        <is>
+          <t>15.81</t>
+        </is>
+      </c>
+      <c r="BW29" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX29" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY29" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ29" t="inlineStr">
+        <is>
+          <t>12284</t>
+        </is>
+      </c>
+      <c r="CA29" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC29" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD29" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="CE29" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="CF29" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="CG29" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="CH29" t="inlineStr">
+        <is>
+          <t>36.35</t>
+        </is>
+      </c>
+      <c r="CI29" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
+        </is>
+      </c>
+      <c r="CJ29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>492.79</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-1.7</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>32.35</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2025-08-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>43.15</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>-9.85</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>-15.62</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>93.33</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>97.78</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>-4.8</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>-3.07</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>38.42</t>
+        </is>
+      </c>
+      <c r="AM30" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>39.92</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>41.18</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>41.20</t>
+        </is>
+      </c>
+      <c r="AQ30" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>-129.55</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>148998047.268034</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>19156578.0</t>
+        </is>
+      </c>
+      <c r="AX30" t="n">
+        <v>69426442.8</v>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>52456837.4</t>
+        </is>
+      </c>
+      <c r="AZ30" t="n">
+        <v>33433682.52</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>16969605</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>4345764.102201018</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>800558.8333693519</t>
+        </is>
+      </c>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>19156578.0</t>
+        </is>
+      </c>
+      <c r="BE30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF30" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG30" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>-6.27</t>
+        </is>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ30" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK30" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL30" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM30" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN30" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO30" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP30" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ30" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR30" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS30" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="BT30" t="inlineStr">
+        <is>
+          <t>6.54</t>
+        </is>
+      </c>
+      <c r="BU30" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV30" t="inlineStr">
+        <is>
+          <t>15.81</t>
+        </is>
+      </c>
+      <c r="BW30" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX30" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY30" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ30" t="inlineStr">
+        <is>
+          <t>12284</t>
+        </is>
+      </c>
+      <c r="CA30" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC30" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD30" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="CE30" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="CF30" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="CG30" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="CH30" t="inlineStr">
+        <is>
+          <t>36.35</t>
+        </is>
+      </c>
+      <c r="CI30" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
+        </is>
+      </c>
+      <c r="CJ30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>510.601</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-2.22</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>32.21</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2025-08-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>43.15</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>-9.39</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>-15.62</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>5.44</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>-4.82</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>-2.98</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>38.01000000000001</t>
+        </is>
+      </c>
+      <c r="AM31" t="n">
+        <v>38.04</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>33.12</t>
+        </is>
+      </c>
+      <c r="AQ31" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>-132.60</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>148998047.268034</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>19953309.0</t>
+        </is>
+      </c>
+      <c r="AX31" t="n">
+        <v>73854919.59999999</v>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>55863021.8</t>
+        </is>
+      </c>
+      <c r="AZ31" t="n">
+        <v>33328621.84</v>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>17991897</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>4990346.878352229</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>3809528.634606227</t>
+        </is>
+      </c>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>19953309.0</t>
+        </is>
+      </c>
+      <c r="BE31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF31" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG31" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>-5.78</t>
+        </is>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ31" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK31" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL31" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM31" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN31" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO31" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP31" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ31" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR31" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS31" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BT31" t="inlineStr">
+        <is>
+          <t>6.54</t>
+        </is>
+      </c>
+      <c r="BU31" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV31" t="inlineStr">
+        <is>
+          <t>15.81</t>
+        </is>
+      </c>
+      <c r="BW31" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX31" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY31" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ31" t="inlineStr">
+        <is>
+          <t>12284</t>
+        </is>
+      </c>
+      <c r="CA31" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC31" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD31" t="inlineStr">
+        <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="CE31" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="CF31" t="inlineStr">
+        <is>
+          <t>38.75</t>
+        </is>
+      </c>
+      <c r="CG31" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="CH31" t="inlineStr">
+        <is>
+          <t>36.35</t>
+        </is>
+      </c>
+      <c r="CI31" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
+        </is>
+      </c>
+      <c r="CJ31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>914.803</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-2.22</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>35.32</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2025-08-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>43.15</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>-9.39</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>-15.62</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>9.75</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AH32" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>-4.88</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>-2.87</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>37.47</t>
+        </is>
+      </c>
+      <c r="AM32" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>40.03</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>41.21</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>20.99</t>
+        </is>
+      </c>
+      <c r="AQ32" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>-135.29</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>148998047.268034</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>35810040.0</t>
+        </is>
+      </c>
+      <c r="AX32" t="n">
+        <v>75499582.59999999</v>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>55792550.2</t>
+        </is>
+      </c>
+      <c r="AZ32" t="n">
+        <v>33454972.78</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>19707032</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>5205041.104487866</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>7886638.29228013</t>
+        </is>
+      </c>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>35810040.0</t>
+        </is>
+      </c>
+      <c r="BE32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF32" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG32" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>-5.78</t>
+        </is>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ32" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK32" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL32" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM32" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN32" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO32" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP32" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ32" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR32" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BS32" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BT32" t="inlineStr">
+        <is>
+          <t>6.54</t>
+        </is>
+      </c>
+      <c r="BU32" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV32" t="inlineStr">
+        <is>
+          <t>15.81</t>
+        </is>
+      </c>
+      <c r="BW32" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX32" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY32" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ32" t="inlineStr">
+        <is>
+          <t>12284</t>
+        </is>
+      </c>
+      <c r="CA32" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB32" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC32" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD32" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="CE32" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="CF32" t="inlineStr">
+        <is>
+          <t>38.15</t>
+        </is>
+      </c>
+      <c r="CG32" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="CH32" t="inlineStr">
+        <is>
+          <t>36.35</t>
+        </is>
+      </c>
+      <c r="CI32" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
+        </is>
+      </c>
+      <c r="CJ32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1043.085</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>41.43</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2025-08-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>43.15</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>-11.70</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>-15.62</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>59.17</t>
+        </is>
+      </c>
+      <c r="AH33" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>-4.89</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>-2.80</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>36.87</t>
+        </is>
+      </c>
+      <c r="AM33" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>40.07</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>41.23</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>5.10</t>
+        </is>
+      </c>
+      <c r="AQ33" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>-137.15</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>148998047.268034</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>39561838.0</t>
+        </is>
+      </c>
+      <c r="AX33" t="n">
+        <v>77102277.8</v>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>54515793.2</t>
+        </is>
+      </c>
+      <c r="AZ33" t="n">
+        <v>33864219.92</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>22586484</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>4717477.979434728</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>11730479.54280426</t>
+        </is>
+      </c>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>39561838.0</t>
+        </is>
+      </c>
+      <c r="BE33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF33" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG33" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>-8.19</t>
+        </is>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ33" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK33" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL33" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM33" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN33" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO33" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP33" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ33" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR33" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS33" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="BT33" t="inlineStr">
+        <is>
+          <t>6.54</t>
+        </is>
+      </c>
+      <c r="BU33" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV33" t="inlineStr">
+        <is>
+          <t>15.81</t>
+        </is>
+      </c>
+      <c r="BW33" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX33" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY33" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ33" t="inlineStr">
+        <is>
+          <t>12284</t>
+        </is>
+      </c>
+      <c r="CA33" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC33" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD33" t="inlineStr">
+        <is>
+          <t>37.05</t>
+        </is>
+      </c>
+      <c r="CE33" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CF33" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CG33" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="CH33" t="inlineStr">
+        <is>
+          <t>36.35</t>
+        </is>
+      </c>
+      <c r="CI33" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
+        </is>
+      </c>
+      <c r="CJ33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>6301.223</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>36.9</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>29.52</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2025-08-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>43.15</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>-14.48</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>-15.62</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>67.14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>-1.63</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM34" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ34" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>148998047.268034</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX34" t="n">
+        <v>74142370</v>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ34" t="n">
+        <v>34130931.06</v>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="BE34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF34" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG34" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ34" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK34" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL34" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM34" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN34" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO34" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP34" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ34" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR34" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS34" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT34" t="inlineStr">
+        <is>
+          <t>6.54</t>
+        </is>
+      </c>
+      <c r="BU34" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV34" t="inlineStr">
+        <is>
+          <t>15.81</t>
+        </is>
+      </c>
+      <c r="BW34" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX34" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY34" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+      <c r="BZ34" t="inlineStr">
+        <is>
+          <t>12284</t>
+        </is>
+      </c>
+      <c r="CA34" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB34" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC34" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD34" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE34" t="inlineStr">
+        <is>
+          <t>37.5</t>
+        </is>
+      </c>
+      <c r="CF34" t="inlineStr">
+        <is>
+          <t>36.9</t>
+        </is>
+      </c>
+      <c r="CG34" t="inlineStr">
+        <is>
+          <t>36.9</t>
+        </is>
+      </c>
+      <c r="CH34" t="inlineStr">
+        <is>
+          <t>36.35</t>
+        </is>
+      </c>
+      <c r="CI34" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 裁剪加工** 建材營造 - 基礎工程、結構工程** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 鋼材、塔架、其他配件</t>
+        </is>
+      </c>
+      <c r="CJ34" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/基礎工程.xlsx
+++ b/Result/checksun_type/基礎工程.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-27.42</t>
+          <t>-42.75</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-19.13</t>
+          <t>-19.41</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,38 +1019,38 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>79.12</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.24</v>
+        <v>-0.48</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AM2" t="n">
@@ -1061,19 +1061,19 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>3252.25</t>
+          <t>482.12</t>
         </is>
       </c>
       <c r="AQ2" t="n">
         <v>0.05</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-100.04</t>
+          <t>-99.83</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1901.780604133545</t>
+          <t>1899.035714285714</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>118.6</v>
+        <v>94</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>163.4</t>
+          <t>164.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>354.26</v>
+        <v>332.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-44</t>
+          <t>-70</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-32.06693219302908</t>
+          <t>-33.45021125752899</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-41.40080431663503</t>
+          <t>-41.05824611227848</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>206.79</t>
+          <t>206.07</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-19.10</t>
+          <t>-27.42</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-18.02</t>
+          <t>-19.13</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1441,61 +1441,61 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>79.12</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>1.24</v>
+        <v>-0.24</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>28.76</v>
+        <v>28.78</v>
       </c>
       <c r="AN3" t="n">
         <v>28.81</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>419.05</t>
+          <t>3252.25</t>
         </is>
       </c>
       <c r="AQ3" t="n">
         <v>0.05</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-100.32</t>
+          <t>-100.04</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1901.780604133545</t>
+          <t>1899.035714285714</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>244.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>147</v>
+        <v>118.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>181.7</t>
+          <t>163.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>350.92</v>
+        <v>354.26</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-34</t>
+          <t>-44</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-30.36986453419164</t>
+          <t>-32.06693219302908</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-54.23300159726458</t>
+          <t>-41.40080431663503</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>244.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>206.79</t>
+          <t>206.07</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,42 +1727,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>29.35</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-1.73</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>28.9</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-19.10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-19.27</t>
+          <t>-18.02</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1863,28 +1863,28 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>82.75</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.31</v>
+        <v>1.24</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.22</v>
+        <v>0.78</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1894,30 +1894,30 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>28.75</v>
+        <v>28.76</v>
       </c>
       <c r="AN4" t="n">
         <v>28.81</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>109.34</t>
+          <t>419.05</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-100.66</t>
+          <t>-100.32</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,24 +1936,24 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1901.780604133545</t>
+          <t>1899.035714285714</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>170.6</v>
+        <v>147</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>205.1</t>
+          <t>181.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>353.42</v>
+        <v>350.92</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -1962,17 +1962,17 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-26.03111234090565</t>
+          <t>-30.36986453419164</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-52.62781908397588</t>
+          <t>-54.23300159726458</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>206.79</t>
+          <t>206.07</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2295,32 +2295,32 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>73.43</t>
+          <t>82.75</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.59</v>
+        <v>0.31</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.11</v>
+        <v>0.22</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>28.76</v>
+        <v>28.75</v>
       </c>
       <c r="AN5" t="n">
         <v>28.81</v>
@@ -2332,14 +2332,14 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>73.39</t>
+          <t>109.34</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-100.84</t>
+          <t>-100.66</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1901.780604133545</t>
+          <t>1899.035714285714</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>200</v>
+        <v>170.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>210.9</t>
+          <t>205.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>355.08</v>
+        <v>353.42</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-34</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-21.19534747852924</t>
+          <t>-26.03111234090565</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-40.95513624056434</t>
+          <t>-52.62781908397588</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>206.79</t>
+          <t>206.07</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,17 +2524,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-18.99</t>
+          <t>-19.27</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2707,45 +2707,45 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>73.43</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>1.19</v>
+        <v>0.59</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.34</v>
+        <v>-0.11</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="AM6" t="n">
         <v>28.76</v>
       </c>
       <c r="AN6" t="n">
-        <v>28.82</v>
+        <v>28.81</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>73.39</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-100.99</t>
+          <t>-100.84</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1901.780604133545</t>
+          <t>1899.035714285714</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>238.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>234.4</v>
+        <v>200</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>257.1</t>
+          <t>210.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>363.88</v>
+        <v>355.08</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-17.60265861270468</t>
+          <t>-21.19534747852924</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-25.28147731281342</t>
+          <t>-40.95513624056434</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>238.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>206.79</t>
+          <t>206.07</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-47.24</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-19.55</t>
+          <t>-18.99</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3129,24 +3129,24 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>84.62</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.84</v>
+        <v>1.19</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.65</v>
+        <v>-0.34</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -3155,19 +3155,19 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>28.75</v>
+        <v>28.76</v>
       </c>
       <c r="AN7" t="n">
-        <v>28.81</v>
+        <v>28.82</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3176,11 +3176,11 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>41.24</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="AR7" t="n">
         <v>-0.05</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-101.09</t>
+          <t>-100.99</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1901.780604133545</t>
+          <t>1899.035714285714</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>386.0</t>
+          <t>238.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>208.2</v>
+        <v>234.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>394.6</t>
+          <t>257.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>364.86</v>
+        <v>363.88</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-186</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-16.20650975813945</t>
+          <t>-17.60265861270468</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-24.3804832262831</t>
+          <t>-25.28147731281342</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>386.0</t>
+          <t>238.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.10</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>206.79</t>
+          <t>206.07</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-46.46</t>
+          <t>-47.24</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-20.53</t>
+          <t>-19.55</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3551,58 +3551,58 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-0.18</v>
+        <v>0.84</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.83</v>
+        <v>-0.65</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.56</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>28.74</v>
+        <v>28.75</v>
       </c>
       <c r="AN8" t="n">
         <v>28.81</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-56.08</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="AR8" t="n">
         <v>-0.05</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-101.05</t>
+          <t>-101.09</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1901.780604133545</t>
+          <t>1899.035714285714</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>386.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>216.4</v>
+        <v>208.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>404.2</t>
+          <t>394.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>361.94</v>
+        <v>364.86</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-187</t>
+          <t>-186</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-14.72033276393152</t>
+          <t>-16.20650975813945</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-38.07976013030105</t>
+          <t>-24.3804832262831</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>386.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-7.10</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>206.79</t>
+          <t>206.07</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3795,17 +3795,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>29.9</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>28.45</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-38.75</t>
+          <t>-46.46</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-20.39</t>
+          <t>-20.53</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -3973,61 +3973,61 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-0.38</v>
+        <v>-0.18</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.5</v>
+        <v>-0.83</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>28.61</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>28.75</v>
+        <v>28.74</v>
       </c>
       <c r="AN9" t="n">
-        <v>28.82</v>
+        <v>28.81</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-54.72</t>
+          <t>-56.08</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-100.91</t>
+          <t>-101.05</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1901.780604133545</t>
+          <t>1899.035714285714</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>239.6</v>
+        <v>216.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>391.2</t>
+          <t>404.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>359.34</v>
+        <v>361.94</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-151</t>
+          <t>-187</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-10.47316415186433</t>
+          <t>-14.72033276393152</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-35.71873570281593</t>
+          <t>-38.07976013030105</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>206.79</t>
+          <t>206.07</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-41.49</t>
+          <t>-38.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-20.25</t>
+          <t>-20.39</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4405,14 +4405,14 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-0.63</v>
+        <v>-0.38</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.11</v>
+        <v>-0.5</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -4421,32 +4421,32 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.61</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>28.76</v>
+        <v>28.75</v>
       </c>
       <c r="AN10" t="n">
-        <v>28.83</v>
+        <v>28.82</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-50.42</t>
+          <t>-54.72</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AR10" t="n">
         <v>-0.04</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-100.78</t>
+          <t>-100.91</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1901.780604133545</t>
+          <t>1899.035714285714</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>221.8</v>
+        <v>239.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>379.1</t>
+          <t>391.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>362.54</v>
+        <v>359.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-157</t>
+          <t>-151</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-5.883060233509495</t>
+          <t>-10.47316415186433</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-26.67731738845089</t>
+          <t>-35.71873570281593</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.90</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>206.79</t>
+          <t>206.07</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,42 +4681,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>28.55</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>28.5</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-26.19</t>
+          <t>-41.49</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-20.39</t>
+          <t>-20.25</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4817,45 +4817,45 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.77</v>
+        <v>-0.63</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="AM11" t="n">
         <v>28.76</v>
       </c>
       <c r="AN11" t="n">
-        <v>28.84</v>
+        <v>28.83</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4864,14 +4864,14 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-42.86</t>
+          <t>-50.42</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-100.68</t>
+          <t>-100.78</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,16 +4890,16 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1901.780604133545</t>
+          <t>1899.035714285714</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>279.8</v>
+        <v>221.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
@@ -4907,26 +4907,26 @@
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>366.02</v>
+        <v>362.54</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-99</t>
+          <t>-157</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2.102286205338332</t>
+          <t>-5.883060233509495</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-17.95110131834184</t>
+          <t>-26.67731738845089</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>206.79</t>
+          <t>206.07</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5061,17 +5061,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>28.9</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>28.5</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>28.5</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5093,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>56.31</t>
+          <t>-26.19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5249,48 +5249,48 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>36.67</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-0.63</v>
+        <v>-0.77</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.26</v>
+        <v>-0.12</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>28.72</t>
         </is>
       </c>
       <c r="AM12" t="n">
         <v>28.76</v>
       </c>
       <c r="AN12" t="n">
-        <v>28.85</v>
+        <v>28.84</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-42.86</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="AR12" t="n">
         <v>-0.03</v>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-100.61</t>
+          <t>-100.68</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1901.780604133545</t>
+          <t>1899.035714285714</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>427.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>581</v>
+        <v>279.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>371.7</t>
+          <t>379.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>371.3</v>
+        <v>366.02</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-99</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.7793165424804881</t>
+          <t>-2.102286205338332</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5.227460971754681</t>
+          <t>-17.95110131834184</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>427.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>206.79</t>
+          <t>206.07</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>174.116</t>
+          <t>124.224</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5555,17 +5555,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-35.34</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5635,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5656,12 +5656,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5671,51 +5671,51 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>-1.15</v>
+        <v>-1.03</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.2</v>
+        <v>0.96</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>165.9</t>
+          <t>165.7</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>163.92</v>
+        <v>164.12</v>
       </c>
       <c r="AN13" t="n">
-        <v>163.04</v>
+        <v>163.21</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>159.51</t>
+          <t>159.52</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-14.25</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-87.00</t>
+          <t>-87.86</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5734,48 +5734,48 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>86058090.43493634</t>
+          <t>85979692.83474576</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>28370272.0</t>
+          <t>20368393.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>40590850.2</v>
+        <v>36074581.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>57963626.5</t>
+          <t>55794746.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>74658967.16</v>
+        <v>73577359.40000001</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-17372776</t>
+          <t>-19720165</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-2086698.748341866</t>
+          <t>-2752614.863771097</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-4718060.69371102</t>
+          <t>-6415153.498631865</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>28370272.0</t>
+          <t>20368393.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5900,17 +5900,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>165.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -5937,7 +5937,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>351.96</t>
+          <t>174.116</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-15.05</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6057,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6078,12 +6078,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6093,51 +6093,51 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>-1.32</v>
+        <v>-1.15</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>166.2</t>
+          <t>165.9</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>163.88</v>
+        <v>163.92</v>
       </c>
       <c r="AN14" t="n">
-        <v>162.83</v>
+        <v>163.04</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>159.48</t>
+          <t>159.51</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>-14.25</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-86.54</t>
+          <t>-87.00</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6156,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>86058090.43493634</t>
+          <t>85979692.83474576</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>57673277.0</t>
+          <t>28370272.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>54192712.8</v>
+        <v>40590850.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>63795677.8</t>
+          <t>57963626.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>74797212.08</v>
+        <v>74658967.16</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-9602965</t>
+          <t>-17372776</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-1608269.303729293</t>
+          <t>-2086698.748341866</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-2982484.411905855</t>
+          <t>-4718060.69371102</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>57673277.0</t>
+          <t>28370272.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6322,17 +6322,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>166.5</t>
+          <t>164.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>166.5</t>
+          <t>164.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>168.262</t>
+          <t>351.96</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>167.5</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6394,17 +6394,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-15.05</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6479,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6500,66 +6500,66 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>44.19</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>-0.12</v>
+        <v>-1.32</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.32</v>
+        <v>1.42</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>167.7</t>
+          <t>166.2</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>163.9</v>
+        <v>163.88</v>
       </c>
       <c r="AN15" t="n">
-        <v>162.61</v>
+        <v>162.83</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>159.52</t>
+          <t>159.48</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-86.71</t>
+          <t>-86.54</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6578,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>86058090.43493634</t>
+          <t>85979692.83474576</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>28309050.0</t>
+          <t>57673277.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>57384170</v>
+        <v>54192712.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>64090738.9</t>
+          <t>63795677.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>74355456.31999999</v>
+        <v>74797212.08</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-6706568</t>
+          <t>-9602965</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-1358412.011333554</t>
+          <t>-1608269.303729293</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3536180.101758972</t>
+          <t>-2982484.411905855</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>28309050.0</t>
+          <t>57673277.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6679,17 +6679,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6744,22 +6744,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>166.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>166.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>166.5</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>167.5</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>273.6</t>
+          <t>168.262</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6922,66 +6922,66 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>44.19</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>0.66</v>
+        <v>-0.12</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>167.9</t>
+          <t>167.7</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>163.82</v>
+        <v>163.9</v>
       </c>
       <c r="AN16" t="n">
-        <v>162.31</v>
+        <v>162.61</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>159.51</t>
+          <t>159.52</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AR16" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-87.82</t>
+          <t>-86.71</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7000,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>86058090.43493634</t>
+          <t>85979692.83474576</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>45651915.0</t>
+          <t>28309050.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>69731964.59999999</v>
+        <v>57384170</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>64109050.7</t>
+          <t>64090738.9</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>74583191.94</v>
+        <v>74355456.31999999</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5622913</t>
+          <t>-6706568</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-962454.1767107508</t>
+          <t>-1358412.011333554</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1054714.61934346</t>
+          <t>-3536180.101758972</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>45651915.0</t>
+          <t>28309050.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7101,17 +7101,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>6.70</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7166,22 +7166,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>166.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>260.926</t>
+          <t>273.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7238,17 +7238,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7323,17 +7323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>15.32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7344,66 +7344,66 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>56.33</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>-1.84</v>
+        <v>0.66</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>168.1</t>
+          <t>167.9</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>163.52</v>
+        <v>163.82</v>
       </c>
       <c r="AN17" t="n">
-        <v>162.01</v>
+        <v>162.31</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>159.49</t>
+          <t>159.51</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-89.22</t>
+          <t>-87.82</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7422,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>86058090.43493634</t>
+          <t>85979692.83474576</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>42949737.0</t>
+          <t>45651915.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>75514912.40000001</v>
+        <v>69731964.59999999</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>63397896.3</t>
+          <t>64109050.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>74231801.62</v>
+        <v>74583191.94</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>12117016</t>
+          <t>5622913</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-945679.550777531</t>
+          <t>-962454.1767107508</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>669740.3419409543</t>
+          <t>-1054714.61934346</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>42949737.0</t>
+          <t>45651915.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7523,17 +7523,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.70</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7588,22 +7588,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>166.5</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>163.5</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>577.729</t>
+          <t>260.926</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7660,17 +7660,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7745,17 +7745,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7766,66 +7766,66 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>56.33</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>-1.78</v>
+        <v>-1.84</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>168.1</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>163.35</v>
+        <v>163.52</v>
       </c>
       <c r="AN18" t="n">
-        <v>161.78</v>
+        <v>162.01</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>159.54</t>
+          <t>159.49</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>84.89</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-90.43</t>
+          <t>-89.22</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7844,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>86058090.43493634</t>
+          <t>85979692.83474576</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>96379585.0</t>
+          <t>42949737.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>75336402.8</v>
+        <v>75514912.40000001</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>66225041.0</t>
+          <t>63397896.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>73921052.92</v>
+        <v>74231801.62</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>9111361</t>
+          <t>12117016</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-1239392.258544528</t>
+          <t>-945679.550777531</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>3398847.202992231</t>
+          <t>669740.3419409543</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>96379585.0</t>
+          <t>42949737.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -7945,17 +7945,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8010,22 +8010,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>169.5</t>
+          <t>165.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>166.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
+          <t>163.5</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
           <t>165.0</t>
-        </is>
-      </c>
-      <c r="CG18" t="inlineStr">
-        <is>
-          <t>165.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>432.237</t>
+          <t>577.729</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>171.5</t>
+          <t>165.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8082,17 +8082,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8167,17 +8167,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>24.20</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8188,66 +8188,66 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>76.56</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>1.84</v>
+        <v>-1.78</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>168.5</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>163.32</v>
+        <v>163.35</v>
       </c>
       <c r="AN19" t="n">
-        <v>161.52</v>
+        <v>161.78</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>159.59</t>
+          <t>159.54</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>157.65</t>
+          <t>84.89</t>
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-92.46</t>
+          <t>-90.43</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8266,43 +8266,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>86058090.43493634</t>
+          <t>85979692.83474576</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>73630563.0</t>
+          <t>96379585.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>73398642.8</v>
+        <v>75336402.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>62924758.1</t>
+          <t>66225041.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>72538562.06</v>
+        <v>73921052.92</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>10473884</t>
+          <t>9111361</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-2082708.524278485</t>
+          <t>-1239392.258544528</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1451557.318672895</t>
+          <t>3398847.202992231</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>73630563.0</t>
+          <t>96379585.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8367,17 +8367,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8432,22 +8432,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>169.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>171.5</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>166.5</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>171.5</t>
+          <t>165.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>539.56</t>
+          <t>432.237</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8504,17 +8504,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8589,38 +8589,38 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>30.21</t>
+          <t>24.20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8629,47 +8629,47 @@
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>1.08</v>
+        <v>1.84</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.19</v>
+        <v>3.11</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>166.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>163.12</v>
+        <v>163.32</v>
       </c>
       <c r="AN20" t="n">
-        <v>161.14</v>
+        <v>161.52</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>159.54</t>
+          <t>159.59</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>204.17</t>
+          <t>157.65</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.37</v>
+        <v>0.62</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-95.43</t>
+          <t>-92.46</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8688,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>86058090.43493634</t>
+          <t>85979692.83474576</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>90048023.0</t>
+          <t>73630563.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>70797307.8</v>
+        <v>73398642.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>59245744.4</t>
+          <t>62924758.1</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>71727217.04000001</v>
+        <v>72538562.06</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>11551563</t>
+          <t>10473884</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-2725302.313906008</t>
+          <t>-2082708.524278485</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1055268.508264124</t>
+          <t>1451557.318672895</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>90048023.0</t>
+          <t>73630563.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8789,17 +8789,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -8859,17 +8859,17 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>166.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>441.196</t>
+          <t>539.56</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>168.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8926,17 +8926,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>24.70</t>
+          <t>30.21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9032,66 +9032,66 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>2.66</v>
+        <v>1.08</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.58</v>
+        <v>2.19</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>165.6</t>
+          <t>166.7</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>163.02</v>
+        <v>163.12</v>
       </c>
       <c r="AN21" t="n">
-        <v>160.83</v>
+        <v>161.14</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>159.44</t>
+          <t>159.54</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>363.31</t>
+          <t>204.17</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>0.85</v>
+        <v>1.14</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.18</v>
+        <v>0.37</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-97.76</t>
+          <t>-95.43</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9110,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>86058090.43493634</t>
+          <t>85979692.83474576</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>74566654.0</t>
+          <t>90048023.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>58486136.8</v>
+        <v>70797307.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>58606873.6</t>
+          <t>59245744.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>70642832.02</v>
+        <v>71727217.04000001</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-120736</t>
+          <t>11551563</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-3412678.827027851</t>
+          <t>-2725302.313906008</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1307560.096186429</t>
+          <t>1055268.508264124</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>74566654.0</t>
+          <t>90048023.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9211,17 +9211,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>168.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>168.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>253.751</t>
+          <t>441.196</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9338,74 +9338,74 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>170.0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-07-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>167.0</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-1.83</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-1.77</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>-10.93</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-07-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>167.0</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>164.0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>167.0</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>187.0</t>
@@ -9418,12 +9418,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>24.70</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9454,12 +9454,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9473,47 +9473,47 @@
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>2.02</v>
+        <v>2.66</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.48</v>
+        <v>1.58</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>163.7</t>
+          <t>165.6</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>162.93</v>
+        <v>163.02</v>
       </c>
       <c r="AN22" t="n">
-        <v>160.46</v>
+        <v>160.83</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>159.64</t>
+          <t>159.44</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>1770.32</t>
+          <t>363.31</t>
         </is>
       </c>
       <c r="AQ22" t="n">
-        <v>0.31</v>
+        <v>0.85</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-99.79</t>
+          <t>-97.76</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9532,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>86058090.43493634</t>
+          <t>85979692.83474576</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>42057189.0</t>
+          <t>74566654.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>51280880.2</v>
+        <v>58486136.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>57575110.0</t>
+          <t>58606873.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>70368392.78</v>
+        <v>70642832.02</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-6294229</t>
+          <t>-120736</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-3795427.687180837</t>
+          <t>-3412678.827027851</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-2977612.849109128</t>
+          <t>-1307560.096186429</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>42057189.0</t>
+          <t>74566654.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9698,22 +9698,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
+          <t>170.0</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>167.0</t>
         </is>
       </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>164.0</t>
-        </is>
-      </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9735,7 +9735,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>525.675</t>
+          <t>253.751</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9770,22 +9770,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-11.52</t>
+          <t>-10.93</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -9840,12 +9840,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -9855,33 +9855,33 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>29.43</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -9895,47 +9895,47 @@
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.43</v>
+        <v>0.48</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>163.7</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>163.1</v>
+        <v>162.93</v>
       </c>
       <c r="AN23" t="n">
-        <v>160.23</v>
+        <v>160.46</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>159.91</t>
+          <t>159.64</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-16.36</t>
+          <t>1770.32</t>
         </is>
       </c>
       <c r="AQ23" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="AR23" t="n">
-        <v>-0.06</v>
+        <v>0.02</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-100.70</t>
+          <t>-99.79</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -9954,48 +9954,48 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>86058090.43493634</t>
+          <t>85979692.83474576</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>86690785.0</t>
+          <t>42057189.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>57113679.2</v>
+        <v>51280880.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>64547068.7</t>
+          <t>57575110.0</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>70595791.64</v>
+        <v>70368392.78</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-7433389</t>
+          <t>-6294229</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-3944121.294102966</t>
+          <t>-3795427.687180837</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-1773902.21581623</t>
+          <t>-2977612.849109128</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>86690785.0</t>
+          <t>42057189.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10120,22 +10120,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>325.91</t>
+          <t>389.965</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10197,12 +10197,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-28.68</t>
+          <t>-18.11</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-11.36</t>
+          <t>-12.28</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10277,17 +10277,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10298,12 +10298,12 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -10313,51 +10313,51 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>57.58</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>-1.26</v>
+        <v>-1.79</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.09</v>
+        <v>1.53</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>38.54000000000001</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>37.95</v>
+        <v>37.96</v>
       </c>
       <c r="AN24" t="n">
-        <v>39.48</v>
+        <v>39.39</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>40.87</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>59.95</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="AR24" t="n">
-        <v>-0.35</v>
+        <v>-0.32</v>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-113.14</t>
+          <t>-111.86</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10376,43 +10376,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>148998047.268034</t>
+          <t>148818975.3283898</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>12502974.0</t>
+          <t>14810076.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>14661037.6</v>
+        <v>14807963.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>20557419.7</t>
+          <t>18082243.5</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>32207875.34</v>
+        <v>32163668.02</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-5896382</t>
+          <t>-3274279</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-1246342.232336838</t>
+          <t>-1898654.569142961</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-5563232.276525833</t>
+          <t>-5486372.421576638</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>12502974.0</t>
+          <t>14810076.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="BV24" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>15.64</t>
         </is>
       </c>
       <c r="BW24" t="inlineStr">
@@ -10517,12 +10517,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10542,22 +10542,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10589,12 +10589,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>410.32</t>
+          <t>325.91</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10614,17 +10614,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-63.08</t>
+          <t>-28.68</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-11.36</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10699,17 +10699,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10720,66 +10720,66 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>84.98</t>
+          <t>57.58</t>
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>-1.26</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>37.97</v>
+        <v>37.95</v>
       </c>
       <c r="AN25" t="n">
-        <v>39.56</v>
+        <v>39.48</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>40.93</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>68.34</t>
+          <t>59.95</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="AR25" t="n">
-        <v>-0.41</v>
+        <v>-0.35</v>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-115.10</t>
+          <t>-113.14</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10798,43 +10798,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>148998047.268034</t>
+          <t>148818975.3283898</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>15869530.0</t>
+          <t>12502974.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>15717891.6</v>
+        <v>14661037.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>42572167.2</t>
+          <t>20557419.7</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>32421504.8</v>
+        <v>32207875.34</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-26854275</t>
+          <t>-5896382</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-461453.1333933839</t>
+          <t>-1246342.232336838</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-5227155.702291623</t>
+          <t>-5563232.276525833</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>15869530.0</t>
+          <t>12502974.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="BV25" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>15.64</t>
         </is>
       </c>
       <c r="BW25" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -10964,22 +10964,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>435.235</t>
+          <t>410.32</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11036,17 +11036,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-63.70</t>
+          <t>-63.08</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11121,17 +11121,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11142,66 +11142,66 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>97.73</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>84.98</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>2.32</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>37.98</v>
+        <v>37.97</v>
       </c>
       <c r="AN26" t="n">
-        <v>39.63</v>
+        <v>39.56</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>63.94</t>
+          <t>68.34</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>-0.17</v>
+        <v>-0.13</v>
       </c>
       <c r="AR26" t="n">
-        <v>-0.47</v>
+        <v>-0.41</v>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-117.68</t>
+          <t>-115.10</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11220,43 +11220,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>148998047.268034</t>
+          <t>148818975.3283898</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>16996914.0</t>
+          <t>15869530.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>16375301.2</v>
+        <v>15717891.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>45115110.4</t>
+          <t>42572167.2</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>32578634.98</v>
+        <v>32421504.8</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-28739809</t>
+          <t>-26854275</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>405038.2427699324</t>
+          <t>-461453.1333933839</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-4921064.606875196</t>
+          <t>-5227155.702291623</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>16996914.0</t>
+          <t>15869530.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="BT26" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BU26" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="BV26" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>15.64</t>
         </is>
       </c>
       <c r="BW26" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11386,22 +11386,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>358.496</t>
+          <t>435.235</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11458,17 +11458,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-63.30</t>
+          <t>-63.70</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-10.31</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11543,17 +11543,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11564,66 +11564,66 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>97.73</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>87.65</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>-0.44</v>
+        <v>0.49</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>38.86</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>37.97</v>
+        <v>37.98</v>
       </c>
       <c r="AN27" t="n">
-        <v>39.7</v>
+        <v>39.63</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>55.74</t>
+          <t>63.94</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>-0.24</v>
+        <v>-0.17</v>
       </c>
       <c r="AR27" t="n">
-        <v>-0.55</v>
+        <v>-0.47</v>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-120.51</t>
+          <t>-117.68</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11642,43 +11642,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>148998047.268034</t>
+          <t>148818975.3283898</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>13860324.0</t>
+          <t>16996914.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>16966580.2</v>
+        <v>16375301.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>46233081.4</t>
+          <t>45115110.4</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>32635911.38</v>
+        <v>32578634.98</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-29266501</t>
+          <t>-28739809</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>1373420.579069047</t>
+          <t>405038.2427699324</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-4428830.448891897</t>
+          <t>-4921064.606875196</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>13860324.0</t>
+          <t>16996914.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11753,12 +11753,12 @@
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BU27" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="BV27" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>15.64</t>
         </is>
       </c>
       <c r="BW27" t="inlineStr">
@@ -11783,12 +11783,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -11808,22 +11808,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="CE27" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="CF27" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="CG27" t="inlineStr">
+        <is>
           <t>39.05</t>
-        </is>
-      </c>
-      <c r="CE27" t="inlineStr">
-        <is>
-          <t>39.1</t>
-        </is>
-      </c>
-      <c r="CF27" t="inlineStr">
-        <is>
-          <t>38.45</t>
-        </is>
-      </c>
-      <c r="CG27" t="inlineStr">
-        <is>
-          <t>38.7</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>363.213</t>
+          <t>358.496</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11880,17 +11880,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-56.62</t>
+          <t>-63.30</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-10.31</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -11965,17 +11965,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -11986,66 +11986,66 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>90.74</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>87.65</t>
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>-0.26</v>
+        <v>-0.44</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AM28" t="n">
         <v>37.97</v>
       </c>
       <c r="AN28" t="n">
-        <v>39.78</v>
+        <v>39.7</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>41.08</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>55.74</t>
         </is>
       </c>
       <c r="AQ28" t="n">
-        <v>-0.3</v>
+        <v>-0.24</v>
       </c>
       <c r="AR28" t="n">
-        <v>-0.63</v>
+        <v>-0.55</v>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-123.37</t>
+          <t>-120.51</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12064,43 +12064,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>148998047.268034</t>
+          <t>148818975.3283898</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>14075446.0</t>
+          <t>13860324.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>21356523.4</v>
+        <v>16966580.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>49229400.6</t>
+          <t>46233081.4</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>32854915.68</v>
+        <v>32635911.38</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-27872877</t>
+          <t>-29266501</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>2428375.311425582</t>
+          <t>1373420.579069047</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-3231403.064312473</t>
+          <t>-4428830.448891897</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>14075446.0</t>
+          <t>13860324.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BU28" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="BV28" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>15.64</t>
         </is>
       </c>
       <c r="BW28" t="inlineStr">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12230,22 +12230,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>455.261</t>
+          <t>363.213</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12302,17 +12302,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-47.41</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12387,17 +12387,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12408,66 +12408,66 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.74</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>37.98</v>
+        <v>37.97</v>
       </c>
       <c r="AN29" t="n">
-        <v>39.86</v>
+        <v>39.78</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>-0.38</v>
+        <v>-0.3</v>
       </c>
       <c r="AR29" t="n">
-        <v>-0.71</v>
+        <v>-0.63</v>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-126.44</t>
+          <t>-123.37</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12486,43 +12486,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>148998047.268034</t>
+          <t>148818975.3283898</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>17787244.0</t>
+          <t>14075446.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>26453801.8</v>
+        <v>21356523.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>50298085.9</t>
+          <t>49229400.6</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>33264214.78</v>
+        <v>32854915.68</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-23844284</t>
+          <t>-27872877</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>3457425.925196137</t>
+          <t>2428375.311425582</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-1428434.048330702</t>
+          <t>-3231403.064312473</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>17787244.0</t>
+          <t>14075446.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="BT29" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BU29" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="BV29" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>15.64</t>
         </is>
       </c>
       <c r="BW29" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12652,22 +12652,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="CE29" t="inlineStr">
+        <is>
+          <t>38.95</t>
+        </is>
+      </c>
+      <c r="CF29" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="CE29" t="inlineStr">
-        <is>
-          <t>39.5</t>
-        </is>
-      </c>
-      <c r="CF29" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12699,12 +12699,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>492.79</t>
+          <t>455.261</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12724,17 +12724,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>-47.41</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-9.85</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -12809,17 +12809,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -12830,66 +12830,66 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.1</v>
+        <v>2.16</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>38</v>
+        <v>37.98</v>
       </c>
       <c r="AN30" t="n">
-        <v>39.92</v>
+        <v>39.86</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>41.20</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>-0.47</v>
+        <v>-0.38</v>
       </c>
       <c r="AR30" t="n">
-        <v>-0.79</v>
+        <v>-0.71</v>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-126.44</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -12908,43 +12908,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>148998047.268034</t>
+          <t>148818975.3283898</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>19156578.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>69426442.8</v>
+        <v>26453801.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>52456837.4</t>
+          <t>50298085.9</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>33433682.52</v>
+        <v>33264214.78</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>16969605</t>
+          <t>-23844284</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>4345764.102201018</t>
+          <t>3457425.925196137</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>800558.8333693519</t>
+          <t>-1428434.048330702</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>19156578.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="BT30" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BU30" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="BV30" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>15.64</t>
         </is>
       </c>
       <c r="BW30" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13074,12 +13074,12 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13111,7 +13111,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13121,12 +13121,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>510.601</t>
+          <t>492.79</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13146,17 +13146,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-9.39</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13231,17 +13231,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13252,66 +13252,66 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>2.87</v>
+        <v>1.25</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.09</v>
+        <v>1.1</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>38.01000000000001</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>38.04</v>
+        <v>38</v>
       </c>
       <c r="AN31" t="n">
-        <v>39.97</v>
+        <v>39.92</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>41.20</t>
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>-0.59</v>
+        <v>-0.47</v>
       </c>
       <c r="AR31" t="n">
-        <v>-0.88</v>
+        <v>-0.79</v>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13330,43 +13330,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>148998047.268034</t>
+          <t>148818975.3283898</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>73854919.59999999</v>
+        <v>69426442.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>55863021.8</t>
+          <t>52456837.4</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>33328621.84</v>
+        <v>33433682.52</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>17991897</t>
+          <t>16969605</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>4990346.878352229</t>
+          <t>4345764.102201018</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>3809528.634606227</t>
+          <t>800558.8333693519</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13431,22 +13431,22 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BU31" t="inlineStr">
@@ -13456,7 +13456,7 @@
       </c>
       <c r="BV31" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>15.64</t>
         </is>
       </c>
       <c r="BW31" t="inlineStr">
@@ -13471,12 +13471,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13496,22 +13496,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>914.803</t>
+          <t>510.601</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13568,17 +13568,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13674,12 +13674,12 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -13689,51 +13689,51 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>4.35</v>
+        <v>2.87</v>
       </c>
       <c r="AI32" t="n">
-        <v>-1.59</v>
+        <v>-0.09</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>38.01000000000001</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>38.08</v>
+        <v>38.04</v>
       </c>
       <c r="AN32" t="n">
-        <v>40.03</v>
+        <v>39.97</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>-0.75</v>
+        <v>-0.59</v>
       </c>
       <c r="AR32" t="n">
-        <v>-0.95</v>
+        <v>-0.88</v>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-135.29</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -13752,43 +13752,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>148998047.268034</t>
+          <t>148818975.3283898</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>75499582.59999999</v>
+        <v>73854919.59999999</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>55792550.2</t>
+          <t>55863021.8</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>33454972.78</v>
+        <v>33328621.84</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>19707032</t>
+          <t>17991897</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>5205041.104487866</t>
+          <t>4990346.878352229</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>7886638.29228013</t>
+          <t>3809528.634606227</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -13853,7 +13853,7 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="BT32" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BU32" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="BV32" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>15.64</t>
         </is>
       </c>
       <c r="BW32" t="inlineStr">
@@ -13893,12 +13893,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -13918,17 +13918,17 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1043.085</t>
+          <t>914.803</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -13990,17 +13990,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14075,17 +14075,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14096,12 +14096,12 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -14111,52 +14111,52 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>3.34</v>
+        <v>4.35</v>
       </c>
       <c r="AI33" t="n">
-        <v>-3.27</v>
+        <v>-1.59</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>38.11</v>
+        <v>38.08</v>
       </c>
       <c r="AN33" t="n">
-        <v>40.07</v>
+        <v>40.03</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AQ33" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AR33" t="n">
         <v>-0.95</v>
       </c>
-      <c r="AR33" t="n">
-        <v>-1</v>
-      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>2.69</t>
@@ -14164,7 +14164,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-137.15</t>
+          <t>-135.29</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14174,43 +14174,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>148998047.268034</t>
+          <t>148818975.3283898</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>77102277.8</v>
+        <v>75499582.59999999</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>54515793.2</t>
+          <t>55792550.2</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>33864219.92</v>
+        <v>33454972.78</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>22586484</t>
+          <t>19707032</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>4717477.979434728</t>
+          <t>5205041.104487866</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>11730479.54280426</t>
+          <t>7886638.29228013</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14285,12 +14285,12 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BU33" t="inlineStr">
@@ -14300,7 +14300,7 @@
       </c>
       <c r="BV33" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>15.64</t>
         </is>
       </c>
       <c r="BW33" t="inlineStr">
@@ -14315,12 +14315,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14340,22 +14340,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14377,7 +14377,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -14387,12 +14387,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6301.223</t>
+          <t>1043.085</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14412,17 +14412,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14497,17 +14497,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14518,66 +14518,66 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>59.17</t>
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>0.82</v>
+        <v>3.34</v>
       </c>
       <c r="AI34" t="n">
-        <v>-4.24</v>
+        <v>-3.27</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>36.60000000000001</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>38.22</v>
+        <v>38.11</v>
       </c>
       <c r="AN34" t="n">
-        <v>40.17</v>
+        <v>40.07</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AQ34" t="n">
-        <v>-1.08</v>
+        <v>-0.95</v>
       </c>
       <c r="AR34" t="n">
-        <v>-1.01</v>
+        <v>-1</v>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-137.62</t>
+          <t>-137.15</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14596,43 +14596,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>148998047.268034</t>
+          <t>148818975.3283898</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>74142370</v>
+        <v>77102277.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>57245793.0</t>
+          <t>54515793.2</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>34130931.06</v>
+        <v>33864219.92</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>16896577</t>
+          <t>22586484</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>3442386.786094812</t>
+          <t>4717477.979434728</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>16400757.27416717</t>
+          <t>11730479.54280426</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14707,12 +14707,12 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="BV34" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>15.64</t>
         </is>
       </c>
       <c r="BW34" t="inlineStr">
@@ -14737,12 +14737,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -14762,22 +14762,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
+          <t>37.05</t>
+        </is>
+      </c>
+      <c r="CE34" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CF34" t="inlineStr">
+        <is>
           <t>37.0</t>
         </is>
       </c>
-      <c r="CE34" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="CF34" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/基礎工程.xlsx
+++ b/Result/checksun_type/基礎工程.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-32.63</t>
+          <t>-25.81</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,24 +1019,24 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-1.14</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -1045,32 +1045,32 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>28.87</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>28.77</v>
+        <v>28.76</v>
       </c>
       <c r="AN2" t="n">
-        <v>28.8</v>
+        <v>28.79</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>107.66</t>
+          <t>-60.12</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
         <v>0.01</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-99.77</t>
+          <t>-99.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1896.185419968304</t>
+          <t>1893.1875</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>101.6</v>
+        <v>100.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>150.8</t>
+          <t>135.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>331.48</v>
+        <v>329.18</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-49</t>
+          <t>-35</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-34.97971709735867</t>
+          <t>-37.11988776067454</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-43.39199921642194</t>
+          <t>-48.89082640891179</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,17 +1258,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-42.75</t>
+          <t>-32.63</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-19.41</t>
+          <t>-20.11</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1441,58 +1441,58 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.48</v>
+        <v>-1.14</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>28.78</v>
+        <v>28.77</v>
       </c>
       <c r="AN3" t="n">
-        <v>28.81</v>
+        <v>28.8</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>482.12</t>
+          <t>107.66</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="AR3" t="n">
         <v>0.01</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-99.83</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1896.185419968304</t>
+          <t>1893.1875</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>94</v>
+        <v>101.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>164.2</t>
+          <t>150.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>332.54</v>
+        <v>331.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-70</t>
+          <t>-49</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-33.45021125752899</t>
+          <t>-34.97971709735867</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-41.05824611227848</t>
+          <t>-43.39199921642194</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-27.42</t>
+          <t>-42.75</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-19.13</t>
+          <t>-19.41</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1863,38 +1863,38 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>79.12</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.24</v>
+        <v>-0.48</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AM4" t="n">
@@ -1905,19 +1905,19 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>3252.25</t>
+          <t>482.12</t>
         </is>
       </c>
       <c r="AQ4" t="n">
         <v>0.05</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-100.04</t>
+          <t>-99.83</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1896.185419968304</t>
+          <t>1893.1875</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>118.6</v>
+        <v>94</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>163.4</t>
+          <t>164.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>354.26</v>
+        <v>332.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-44</t>
+          <t>-70</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-32.06693219302908</t>
+          <t>-33.45021125752899</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-41.40080431663503</t>
+          <t>-41.05824611227848</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>244.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-19.10</t>
+          <t>-27.42</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-18.02</t>
+          <t>-19.13</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2285,61 +2285,61 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>79.12</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>1.24</v>
+        <v>-0.24</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>28.76</v>
+        <v>28.78</v>
       </c>
       <c r="AN5" t="n">
         <v>28.81</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>419.05</t>
+          <t>3252.25</t>
         </is>
       </c>
       <c r="AQ5" t="n">
         <v>0.05</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-100.32</t>
+          <t>-100.04</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1896.185419968304</t>
+          <t>1893.1875</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>244.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>147</v>
+        <v>118.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>181.7</t>
+          <t>163.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>350.92</v>
+        <v>354.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-34</t>
+          <t>-44</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-30.36986453419164</t>
+          <t>-32.06693219302908</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-54.23300159726458</t>
+          <t>-41.40080431663503</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>244.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,42 +2571,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>29.35</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.21</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>28.9</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-19.10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-19.27</t>
+          <t>-18.02</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2707,28 +2707,28 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>82.75</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.31</v>
+        <v>1.24</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.22</v>
+        <v>0.78</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2738,30 +2738,30 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>28.75</v>
+        <v>28.76</v>
       </c>
       <c r="AN6" t="n">
         <v>28.81</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>109.34</t>
+          <t>419.05</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-100.66</t>
+          <t>-100.32</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,24 +2780,24 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1896.185419968304</t>
+          <t>1893.1875</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>170.6</v>
+        <v>147</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>205.1</t>
+          <t>181.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>353.42</v>
+        <v>350.92</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2806,17 +2806,17 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-26.03111234090565</t>
+          <t>-30.36986453419164</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-52.62781908397588</t>
+          <t>-54.23300159726458</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3139,32 +3139,32 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>73.43</t>
+          <t>82.75</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.59</v>
+        <v>0.31</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.11</v>
+        <v>0.22</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>28.76</v>
+        <v>28.75</v>
       </c>
       <c r="AN7" t="n">
         <v>28.81</v>
@@ -3176,14 +3176,14 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>73.39</t>
+          <t>109.34</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-100.84</t>
+          <t>-100.66</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1896.185419968304</t>
+          <t>1893.1875</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>200</v>
+        <v>170.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>210.9</t>
+          <t>205.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>355.08</v>
+        <v>353.42</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-34</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-21.19534747852924</t>
+          <t>-26.03111234090565</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-40.95513624056434</t>
+          <t>-52.62781908397588</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,17 +3368,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.83</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-18.99</t>
+          <t>-19.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3551,45 +3551,45 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>73.43</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.19</v>
+        <v>0.59</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.34</v>
+        <v>-0.11</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="AM8" t="n">
         <v>28.76</v>
       </c>
       <c r="AN8" t="n">
-        <v>28.82</v>
+        <v>28.81</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3598,14 +3598,14 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>73.39</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-100.99</t>
+          <t>-100.84</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1896.185419968304</t>
+          <t>1893.1875</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>238.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>234.4</v>
+        <v>200</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>257.1</t>
+          <t>210.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>363.88</v>
+        <v>355.08</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-17.60265861270468</t>
+          <t>-21.19534747852924</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-25.28147731281342</t>
+          <t>-40.95513624056434</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>238.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-47.24</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-19.55</t>
+          <t>-18.99</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3973,24 +3973,24 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>84.62</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.84</v>
+        <v>1.19</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.65</v>
+        <v>-0.34</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -3999,19 +3999,19 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>28.75</v>
+        <v>28.76</v>
       </c>
       <c r="AN9" t="n">
-        <v>28.81</v>
+        <v>28.82</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4020,11 +4020,11 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>41.24</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="AR9" t="n">
         <v>-0.05</v>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.09</t>
+          <t>-100.99</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1896.185419968304</t>
+          <t>1893.1875</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>386.0</t>
+          <t>238.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>208.2</v>
+        <v>234.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>394.6</t>
+          <t>257.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>364.86</v>
+        <v>363.88</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-186</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-16.20650975813945</t>
+          <t>-17.60265861270468</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-24.3804832262831</t>
+          <t>-25.28147731281342</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>386.0</t>
+          <t>238.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.10</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-46.46</t>
+          <t>-47.24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-20.53</t>
+          <t>-19.55</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4395,58 +4395,58 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-0.18</v>
+        <v>0.84</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.83</v>
+        <v>-0.65</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.56</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>28.74</v>
+        <v>28.75</v>
       </c>
       <c r="AN10" t="n">
         <v>28.81</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-56.08</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="AR10" t="n">
         <v>-0.05</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.05</t>
+          <t>-101.09</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1896.185419968304</t>
+          <t>1893.1875</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>386.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>216.4</v>
+        <v>208.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>404.2</t>
+          <t>394.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>361.94</v>
+        <v>364.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-187</t>
+          <t>-186</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-14.72033276393152</t>
+          <t>-16.20650975813945</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-38.07976013030105</t>
+          <t>-24.3804832262831</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>386.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-7.10</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4639,17 +4639,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>29.9</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>28.45</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-38.75</t>
+          <t>-46.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-20.39</t>
+          <t>-20.53</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -4817,61 +4817,61 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.38</v>
+        <v>-0.18</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.5</v>
+        <v>-0.83</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>28.61</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>28.75</v>
+        <v>28.74</v>
       </c>
       <c r="AN11" t="n">
-        <v>28.82</v>
+        <v>28.81</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-54.72</t>
+          <t>-56.08</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-100.91</t>
+          <t>-101.05</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1896.185419968304</t>
+          <t>1893.1875</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>239.6</v>
+        <v>216.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>391.2</t>
+          <t>404.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>359.34</v>
+        <v>361.94</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-151</t>
+          <t>-187</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-10.47316415186433</t>
+          <t>-14.72033276393152</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-35.71873570281593</t>
+          <t>-38.07976013030105</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-41.49</t>
+          <t>-38.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-20.25</t>
+          <t>-20.39</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5249,14 +5249,14 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-0.63</v>
+        <v>-0.38</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.11</v>
+        <v>-0.5</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -5265,32 +5265,32 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.61</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>28.76</v>
+        <v>28.75</v>
       </c>
       <c r="AN12" t="n">
-        <v>28.83</v>
+        <v>28.82</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-50.42</t>
+          <t>-54.72</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AR12" t="n">
         <v>-0.04</v>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-100.78</t>
+          <t>-100.91</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1896.185419968304</t>
+          <t>1893.1875</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>221.8</v>
+        <v>239.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>379.1</t>
+          <t>391.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>362.54</v>
+        <v>359.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-157</t>
+          <t>-151</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-5.883060233509495</t>
+          <t>-10.47316415186433</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-26.67731738845089</t>
+          <t>-35.71873570281593</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.90</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>202.205</t>
+          <t>228.352</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-34.99</t>
+          <t>-23.61</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5635,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11.32</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5656,17 +5656,17 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -5675,47 +5675,47 @@
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>-0.18</v>
+        <v>-0.06</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.23</v>
+        <v>-0.38</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>164.8</t>
+          <t>164.1</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>164.42</v>
+        <v>164.72</v>
       </c>
       <c r="AN13" t="n">
-        <v>163.39</v>
+        <v>163.58</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>159.59</t>
+          <t>159.68</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-35.99</t>
+          <t>-46.42</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>0.58</v>
+        <v>0.44</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-88.87</t>
+          <t>-90.02</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5734,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>85928636.23624824</t>
+          <t>85887316.12605634</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>33187043.0</t>
+          <t>37727572.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>33581607</v>
+        <v>35465311.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>51656785.8</t>
+          <t>46424740.7</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>73670279.44</v>
+        <v>73904729.36</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-18075178</t>
+          <t>-10959429</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3326265.019284875</t>
+          <t>-3741470.222614978</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-6481340.874610655</t>
+          <t>-6025098.840930544</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>33187043.0</t>
+          <t>37727572.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5835,22 +5835,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.52</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>51113</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5905,17 +5905,17 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>163.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>124.224</t>
+          <t>202.205</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5962,69 +5962,69 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>164.5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-34.99</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-07-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>164.0</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-2.45</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-35.34</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-07-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>167.0</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>164.0</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>0</t>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6057,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6078,66 +6078,66 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>-1.03</v>
+        <v>-0.18</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.96</v>
+        <v>0.23</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>165.7</t>
+          <t>164.8</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>164.12</v>
+        <v>164.42</v>
       </c>
       <c r="AN14" t="n">
-        <v>163.21</v>
+        <v>163.39</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>159.52</t>
+          <t>159.59</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-35.99</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>0.71</v>
+        <v>0.58</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-87.86</t>
+          <t>-88.87</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6156,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>85928636.23624824</t>
+          <t>85887316.12605634</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>20368393.0</t>
+          <t>33187043.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>36074581.4</v>
+        <v>33581607</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>55794746.9</t>
+          <t>51656785.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>73577359.40000001</v>
+        <v>73670279.44</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-19720165</t>
+          <t>-18075178</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-2752614.863771097</t>
+          <t>-3326265.019284875</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-6415153.498631865</t>
+          <t>-6481340.874610655</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>20368393.0</t>
+          <t>33187043.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.52</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>51113</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6322,12 +6322,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>164.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>164.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>174.116</t>
+          <t>124.224</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6394,22 +6394,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-35.34</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6479,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6500,12 +6500,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6515,51 +6515,51 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>-1.15</v>
+        <v>-1.03</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.2</v>
+        <v>0.96</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>165.9</t>
+          <t>165.7</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>163.92</v>
+        <v>164.12</v>
       </c>
       <c r="AN15" t="n">
-        <v>163.04</v>
+        <v>163.21</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>159.51</t>
+          <t>159.52</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-14.25</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-87.00</t>
+          <t>-87.86</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6578,48 +6578,48 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>85928636.23624824</t>
+          <t>85887316.12605634</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>28370272.0</t>
+          <t>20368393.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>40590850.2</v>
+        <v>36074581.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>57963626.5</t>
+          <t>55794746.9</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>74658967.16</v>
+        <v>73577359.40000001</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-17372776</t>
+          <t>-19720165</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-2086698.748341866</t>
+          <t>-2752614.863771097</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-4718060.69371102</t>
+          <t>-6415153.498631865</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>28370272.0</t>
+          <t>20368393.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.52</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>51113</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6744,17 +6744,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>165.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6781,7 +6781,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>351.96</t>
+          <t>174.116</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-15.05</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6922,12 +6922,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -6937,51 +6937,51 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>-1.32</v>
+        <v>-1.15</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>166.2</t>
+          <t>165.9</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>163.88</v>
+        <v>163.92</v>
       </c>
       <c r="AN16" t="n">
-        <v>162.83</v>
+        <v>163.04</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>159.48</t>
+          <t>159.51</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>-14.25</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-86.54</t>
+          <t>-87.00</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7000,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>85928636.23624824</t>
+          <t>85887316.12605634</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>57673277.0</t>
+          <t>28370272.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>54192712.8</v>
+        <v>40590850.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>63795677.8</t>
+          <t>57963626.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>74797212.08</v>
+        <v>74658967.16</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-9602965</t>
+          <t>-17372776</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-1608269.303729293</t>
+          <t>-2086698.748341866</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-2982484.411905855</t>
+          <t>-4718060.69371102</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>57673277.0</t>
+          <t>28370272.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.52</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>51113</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7166,17 +7166,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>166.5</t>
+          <t>164.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>166.5</t>
+          <t>164.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>168.262</t>
+          <t>351.96</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>167.5</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7238,17 +7238,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-15.05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7323,17 +7323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7344,66 +7344,66 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>44.19</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>-0.12</v>
+        <v>-1.32</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.32</v>
+        <v>1.42</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>167.7</t>
+          <t>166.2</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>163.9</v>
+        <v>163.88</v>
       </c>
       <c r="AN17" t="n">
-        <v>162.61</v>
+        <v>162.83</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>159.52</t>
+          <t>159.48</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-86.71</t>
+          <t>-86.54</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7422,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>85928636.23624824</t>
+          <t>85887316.12605634</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>28309050.0</t>
+          <t>57673277.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>57384170</v>
+        <v>54192712.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>64090738.9</t>
+          <t>63795677.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>74355456.31999999</v>
+        <v>74797212.08</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-6706568</t>
+          <t>-9602965</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-1358412.011333554</t>
+          <t>-1608269.303729293</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3536180.101758972</t>
+          <t>-2982484.411905855</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>28309050.0</t>
+          <t>57673277.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7523,22 +7523,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.52</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7563,12 +7563,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>51113</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7588,22 +7588,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>166.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>166.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>166.5</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>167.5</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>273.6</t>
+          <t>168.262</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7660,17 +7660,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7745,17 +7745,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7766,66 +7766,66 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>44.19</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>0.66</v>
+        <v>-0.12</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>167.9</t>
+          <t>167.7</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>163.82</v>
+        <v>163.9</v>
       </c>
       <c r="AN18" t="n">
-        <v>162.31</v>
+        <v>162.61</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>159.51</t>
+          <t>159.52</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AR18" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-87.82</t>
+          <t>-86.71</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7844,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>85928636.23624824</t>
+          <t>85887316.12605634</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>45651915.0</t>
+          <t>28309050.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>69731964.59999999</v>
+        <v>57384170</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>64109050.7</t>
+          <t>64090738.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>74583191.94</v>
+        <v>74355456.31999999</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5622913</t>
+          <t>-6706568</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-962454.1767107508</t>
+          <t>-1358412.011333554</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1054714.61934346</t>
+          <t>-3536180.101758972</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>45651915.0</t>
+          <t>28309050.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -7945,22 +7945,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>6.70</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.52</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>51113</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8010,22 +8010,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>166.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>260.926</t>
+          <t>273.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8082,17 +8082,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8167,17 +8167,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>15.32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8188,66 +8188,66 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>56.33</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>-1.84</v>
+        <v>0.66</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>168.1</t>
+          <t>167.9</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>163.52</v>
+        <v>163.82</v>
       </c>
       <c r="AN19" t="n">
-        <v>162.01</v>
+        <v>162.31</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>159.49</t>
+          <t>159.51</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-89.22</t>
+          <t>-87.82</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8266,43 +8266,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>85928636.23624824</t>
+          <t>85887316.12605634</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>42949737.0</t>
+          <t>45651915.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>75514912.40000001</v>
+        <v>69731964.59999999</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>63397896.3</t>
+          <t>64109050.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>74231801.62</v>
+        <v>74583191.94</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>12117016</t>
+          <t>5622913</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-945679.550777531</t>
+          <t>-962454.1767107508</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>669740.3419409543</t>
+          <t>-1054714.61934346</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>42949737.0</t>
+          <t>45651915.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8367,22 +8367,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.70</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.52</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>51113</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8432,22 +8432,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>166.5</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>163.5</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>577.729</t>
+          <t>260.926</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8589,17 +8589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8610,66 +8610,66 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>56.33</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>-1.78</v>
+        <v>-1.84</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>168.1</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>163.35</v>
+        <v>163.52</v>
       </c>
       <c r="AN20" t="n">
-        <v>161.78</v>
+        <v>162.01</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>159.54</t>
+          <t>159.49</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>84.89</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-90.43</t>
+          <t>-89.22</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8688,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>85928636.23624824</t>
+          <t>85887316.12605634</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>96379585.0</t>
+          <t>42949737.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>75336402.8</v>
+        <v>75514912.40000001</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>66225041.0</t>
+          <t>63397896.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>73921052.92</v>
+        <v>74231801.62</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>9111361</t>
+          <t>12117016</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-1239392.258544528</t>
+          <t>-945679.550777531</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>3398847.202992231</t>
+          <t>669740.3419409543</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>96379585.0</t>
+          <t>42949737.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8789,22 +8789,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.52</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>51113</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -8854,22 +8854,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>169.5</t>
+          <t>165.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>166.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
+          <t>163.5</t>
+        </is>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
           <t>165.0</t>
-        </is>
-      </c>
-      <c r="CG20" t="inlineStr">
-        <is>
-          <t>165.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>432.237</t>
+          <t>577.729</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>171.5</t>
+          <t>165.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8926,17 +8926,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>24.20</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9032,66 +9032,66 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>76.56</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>1.84</v>
+        <v>-1.78</v>
       </c>
       <c r="AI21" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>168.5</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>163.32</v>
+        <v>163.35</v>
       </c>
       <c r="AN21" t="n">
-        <v>161.52</v>
+        <v>161.78</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>159.59</t>
+          <t>159.54</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>157.65</t>
+          <t>84.89</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-92.46</t>
+          <t>-90.43</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9110,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>85928636.23624824</t>
+          <t>85887316.12605634</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>73630563.0</t>
+          <t>96379585.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>73398642.8</v>
+        <v>75336402.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>62924758.1</t>
+          <t>66225041.0</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>72538562.06</v>
+        <v>73921052.92</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>10473884</t>
+          <t>9111361</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-2082708.524278485</t>
+          <t>-1239392.258544528</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1451557.318672895</t>
+          <t>3398847.202992231</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>73630563.0</t>
+          <t>96379585.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.52</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>51113</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>169.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>171.5</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>166.5</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>171.5</t>
+          <t>165.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>539.56</t>
+          <t>432.237</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9348,17 +9348,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9418,12 +9418,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9433,38 +9433,38 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>30.21</t>
+          <t>24.20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9473,47 +9473,47 @@
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>1.08</v>
+        <v>1.84</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.19</v>
+        <v>3.11</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>166.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>163.12</v>
+        <v>163.32</v>
       </c>
       <c r="AN22" t="n">
-        <v>161.14</v>
+        <v>161.52</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>159.54</t>
+          <t>159.59</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>204.17</t>
+          <t>157.65</t>
         </is>
       </c>
       <c r="AQ22" t="n">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.37</v>
+        <v>0.62</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-95.43</t>
+          <t>-92.46</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9532,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>85928636.23624824</t>
+          <t>85887316.12605634</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>90048023.0</t>
+          <t>73630563.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>70797307.8</v>
+        <v>73398642.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>59245744.4</t>
+          <t>62924758.1</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>71727217.04000001</v>
+        <v>72538562.06</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>11551563</t>
+          <t>10473884</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-2725302.313906008</t>
+          <t>-2082708.524278485</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>1055268.508264124</t>
+          <t>1451557.318672895</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>90048023.0</t>
+          <t>73630563.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.52</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>51113</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9703,17 +9703,17 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>166.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>441.196</t>
+          <t>539.56</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>168.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9770,17 +9770,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9840,12 +9840,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -9855,17 +9855,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>24.70</t>
+          <t>30.21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -9876,66 +9876,66 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>2.66</v>
+        <v>1.08</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.58</v>
+        <v>2.19</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>165.6</t>
+          <t>166.7</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>163.02</v>
+        <v>163.12</v>
       </c>
       <c r="AN23" t="n">
-        <v>160.83</v>
+        <v>161.14</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>159.44</t>
+          <t>159.54</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>363.31</t>
+          <t>204.17</t>
         </is>
       </c>
       <c r="AQ23" t="n">
-        <v>0.85</v>
+        <v>1.14</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.18</v>
+        <v>0.37</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-97.76</t>
+          <t>-95.43</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -9954,43 +9954,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>85928636.23624824</t>
+          <t>85887316.12605634</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>74566654.0</t>
+          <t>90048023.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>58486136.8</v>
+        <v>70797307.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>58606873.6</t>
+          <t>59245744.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>70642832.02</v>
+        <v>71727217.04000001</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-120736</t>
+          <t>11551563</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-3412678.827027851</t>
+          <t>-2725302.313906008</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-1307560.096186429</t>
+          <t>1055268.508264124</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>74566654.0</t>
+          <t>90048023.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.52</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>51113</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>168.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>168.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>346.045</t>
+          <t>303.078</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-7.35</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-12.98</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10277,17 +10277,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10298,12 +10298,12 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -10317,44 +10317,44 @@
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>-1.98</v>
+        <v>-1.42</v>
       </c>
       <c r="AI24" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.98999999999999</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>37.93</v>
+        <v>37.9</v>
       </c>
       <c r="AN24" t="n">
-        <v>39.28</v>
+        <v>39.18</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>-0.24</v>
+        <v>-0.28</v>
       </c>
       <c r="AR24" t="n">
         <v>-0.3</v>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-111.24</t>
+          <t>-111.10</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10376,43 +10376,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>148636648.0239774</t>
+          <t>148451284.728169</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>13032611.0</t>
+          <t>11352472.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>14642421</v>
+        <v>13513532.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>15804500.6</t>
+          <t>14944416.9</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>31359427.9</v>
+        <v>31129593.32</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-1162079</t>
+          <t>-1430884</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-2441741.725824472</t>
+          <t>-2893574.929786979</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-5428721.087572783</t>
+          <t>-5378657.551580764</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>13032611.0</t>
+          <t>11352472.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="BM24" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BN24" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="BV24" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="BW24" t="inlineStr">
@@ -10517,12 +10517,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10542,22 +10542,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.25</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10589,12 +10589,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>389.965</t>
+          <t>346.045</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-18.11</t>
+          <t>-7.35</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-12.28</t>
+          <t>-12.98</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10699,17 +10699,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10720,12 +10720,12 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -10735,51 +10735,51 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>-1.79</v>
+        <v>-1.98</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.53</v>
+        <v>1</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>38.54000000000001</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>37.96</v>
+        <v>37.93</v>
       </c>
       <c r="AN25" t="n">
-        <v>39.39</v>
+        <v>39.28</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>-0.18</v>
+        <v>-0.24</v>
       </c>
       <c r="AR25" t="n">
-        <v>-0.32</v>
+        <v>-0.3</v>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-111.86</t>
+          <t>-111.24</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10798,43 +10798,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>148636648.0239774</t>
+          <t>148451284.728169</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>14810076.0</t>
+          <t>13032611.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>14807963.6</v>
+        <v>14642421</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>18082243.5</t>
+          <t>15804500.6</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>32163668.02</v>
+        <v>31359427.9</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-3274279</t>
+          <t>-1162079</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-1898654.569142961</t>
+          <t>-2441741.725824472</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-5486372.421576638</t>
+          <t>-5428721.087572783</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>14810076.0</t>
+          <t>13032611.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="BM25" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BN25" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="BV25" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="BW25" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -10964,22 +10964,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>325.91</t>
+          <t>389.965</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-28.68</t>
+          <t>-18.11</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-11.36</t>
+          <t>-12.28</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11121,17 +11121,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11142,12 +11142,12 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -11157,51 +11157,51 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>57.58</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>-1.26</v>
+        <v>-1.79</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.09</v>
+        <v>1.53</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>38.54000000000001</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>37.95</v>
+        <v>37.96</v>
       </c>
       <c r="AN26" t="n">
-        <v>39.48</v>
+        <v>39.39</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>40.87</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>59.95</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="AR26" t="n">
-        <v>-0.35</v>
+        <v>-0.32</v>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-113.14</t>
+          <t>-111.86</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11220,43 +11220,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>148636648.0239774</t>
+          <t>148451284.728169</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>12502974.0</t>
+          <t>14810076.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>14661037.6</v>
+        <v>14807963.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>20557419.7</t>
+          <t>18082243.5</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>32207875.34</v>
+        <v>32163668.02</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-5896382</t>
+          <t>-3274279</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-1246342.232336838</t>
+          <t>-1898654.569142961</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-5563232.276525833</t>
+          <t>-5486372.421576638</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>12502974.0</t>
+          <t>14810076.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="BM26" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BN26" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -11331,12 +11331,12 @@
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BU26" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="BV26" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="BW26" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11386,22 +11386,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>410.32</t>
+          <t>325.91</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-63.08</t>
+          <t>-28.68</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-11.36</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11543,17 +11543,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11564,66 +11564,66 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>84.98</t>
+          <t>57.58</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>-1.26</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>37.97</v>
+        <v>37.95</v>
       </c>
       <c r="AN27" t="n">
-        <v>39.56</v>
+        <v>39.48</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>40.93</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>68.34</t>
+          <t>59.95</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="AR27" t="n">
-        <v>-0.41</v>
+        <v>-0.35</v>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-115.10</t>
+          <t>-113.14</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11642,43 +11642,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>148636648.0239774</t>
+          <t>148451284.728169</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>15869530.0</t>
+          <t>12502974.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>15717891.6</v>
+        <v>14661037.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>42572167.2</t>
+          <t>20557419.7</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>32421504.8</v>
+        <v>32207875.34</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-26854275</t>
+          <t>-5896382</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-461453.1333933839</t>
+          <t>-1246342.232336838</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-5227155.702291623</t>
+          <t>-5563232.276525833</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>15869530.0</t>
+          <t>12502974.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="BM27" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BN27" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -11753,12 +11753,12 @@
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BU27" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="BV27" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="BW27" t="inlineStr">
@@ -11783,12 +11783,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -11808,22 +11808,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>435.235</t>
+          <t>410.32</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-63.70</t>
+          <t>-63.08</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -11965,17 +11965,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -11986,66 +11986,66 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>97.73</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>84.98</t>
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>2.32</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>37.98</v>
+        <v>37.97</v>
       </c>
       <c r="AN28" t="n">
-        <v>39.63</v>
+        <v>39.56</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>63.94</t>
+          <t>68.34</t>
         </is>
       </c>
       <c r="AQ28" t="n">
-        <v>-0.17</v>
+        <v>-0.13</v>
       </c>
       <c r="AR28" t="n">
-        <v>-0.47</v>
+        <v>-0.41</v>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-117.68</t>
+          <t>-115.10</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12064,43 +12064,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>148636648.0239774</t>
+          <t>148451284.728169</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>16996914.0</t>
+          <t>15869530.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>16375301.2</v>
+        <v>15717891.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>45115110.4</t>
+          <t>42572167.2</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>32578634.98</v>
+        <v>32421504.8</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-28739809</t>
+          <t>-26854275</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>405038.2427699324</t>
+          <t>-461453.1333933839</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-4921064.606875196</t>
+          <t>-5227155.702291623</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>16996914.0</t>
+          <t>15869530.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="BM28" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BN28" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="BT28" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BU28" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="BV28" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="BW28" t="inlineStr">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12230,22 +12230,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>358.496</t>
+          <t>435.235</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-63.30</t>
+          <t>-63.70</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-10.31</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12387,17 +12387,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12408,66 +12408,66 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>97.73</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>87.65</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>-0.44</v>
+        <v>0.49</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>38.86</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>37.97</v>
+        <v>37.98</v>
       </c>
       <c r="AN29" t="n">
-        <v>39.7</v>
+        <v>39.63</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>55.74</t>
+          <t>63.94</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>-0.24</v>
+        <v>-0.17</v>
       </c>
       <c r="AR29" t="n">
-        <v>-0.55</v>
+        <v>-0.47</v>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-120.51</t>
+          <t>-117.68</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12486,43 +12486,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>148636648.0239774</t>
+          <t>148451284.728169</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>13860324.0</t>
+          <t>16996914.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>16966580.2</v>
+        <v>16375301.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>46233081.4</t>
+          <t>45115110.4</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>32635911.38</v>
+        <v>32578634.98</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-29266501</t>
+          <t>-28739809</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>1373420.579069047</t>
+          <t>405038.2427699324</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-4428830.448891897</t>
+          <t>-4921064.606875196</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>13860324.0</t>
+          <t>16996914.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="BM29" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BN29" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BU29" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="BV29" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="BW29" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12652,22 +12652,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="CE29" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="CF29" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="CG29" t="inlineStr">
+        <is>
           <t>39.05</t>
-        </is>
-      </c>
-      <c r="CE29" t="inlineStr">
-        <is>
-          <t>39.1</t>
-        </is>
-      </c>
-      <c r="CF29" t="inlineStr">
-        <is>
-          <t>38.45</t>
-        </is>
-      </c>
-      <c r="CG29" t="inlineStr">
-        <is>
-          <t>38.7</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12699,12 +12699,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>363.213</t>
+          <t>358.496</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-56.62</t>
+          <t>-63.30</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-10.31</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -12809,17 +12809,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -12830,66 +12830,66 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>90.74</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>87.65</t>
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>-0.26</v>
+        <v>-0.44</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AM30" t="n">
         <v>37.97</v>
       </c>
       <c r="AN30" t="n">
-        <v>39.78</v>
+        <v>39.7</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>41.08</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>55.74</t>
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>-0.3</v>
+        <v>-0.24</v>
       </c>
       <c r="AR30" t="n">
-        <v>-0.63</v>
+        <v>-0.55</v>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-123.37</t>
+          <t>-120.51</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -12908,43 +12908,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>148636648.0239774</t>
+          <t>148451284.728169</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>14075446.0</t>
+          <t>13860324.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>21356523.4</v>
+        <v>16966580.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>49229400.6</t>
+          <t>46233081.4</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>32854915.68</v>
+        <v>32635911.38</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-27872877</t>
+          <t>-29266501</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>2428375.311425582</t>
+          <t>1373420.579069047</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-3231403.064312473</t>
+          <t>-4428830.448891897</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>14075446.0</t>
+          <t>13860324.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="BM30" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BN30" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -13019,12 +13019,12 @@
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BU30" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="BV30" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="BW30" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13074,22 +13074,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13121,12 +13121,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>455.261</t>
+          <t>363.213</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-47.41</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13231,17 +13231,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13252,66 +13252,66 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.74</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="AI31" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>37.98</v>
+        <v>37.97</v>
       </c>
       <c r="AN31" t="n">
-        <v>39.86</v>
+        <v>39.78</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>-0.38</v>
+        <v>-0.3</v>
       </c>
       <c r="AR31" t="n">
-        <v>-0.71</v>
+        <v>-0.63</v>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-126.44</t>
+          <t>-123.37</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13330,43 +13330,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>148636648.0239774</t>
+          <t>148451284.728169</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>17787244.0</t>
+          <t>14075446.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>26453801.8</v>
+        <v>21356523.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>50298085.9</t>
+          <t>49229400.6</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>33264214.78</v>
+        <v>32854915.68</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-23844284</t>
+          <t>-27872877</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>3457425.925196137</t>
+          <t>2428375.311425582</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-1428434.048330702</t>
+          <t>-3231403.064312473</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>17787244.0</t>
+          <t>14075446.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="BM31" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BN31" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="BT31" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BU31" t="inlineStr">
@@ -13456,7 +13456,7 @@
       </c>
       <c r="BV31" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="BW31" t="inlineStr">
@@ -13471,12 +13471,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13496,22 +13496,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="CE31" t="inlineStr">
+        <is>
+          <t>38.95</t>
+        </is>
+      </c>
+      <c r="CF31" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="CE31" t="inlineStr">
-        <is>
-          <t>39.5</t>
-        </is>
-      </c>
-      <c r="CF31" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>492.79</t>
+          <t>455.261</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>-47.41</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13643,7 +13643,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-9.85</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13674,66 +13674,66 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.1</v>
+        <v>2.16</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>38</v>
+        <v>37.98</v>
       </c>
       <c r="AN32" t="n">
-        <v>39.92</v>
+        <v>39.86</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>41.20</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>-0.47</v>
+        <v>-0.38</v>
       </c>
       <c r="AR32" t="n">
-        <v>-0.79</v>
+        <v>-0.71</v>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-126.44</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -13752,43 +13752,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>148636648.0239774</t>
+          <t>148451284.728169</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>19156578.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>69426442.8</v>
+        <v>26453801.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>52456837.4</t>
+          <t>50298085.9</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>33433682.52</v>
+        <v>33264214.78</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>16969605</t>
+          <t>-23844284</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>4345764.102201018</t>
+          <t>3457425.925196137</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>800558.8333693519</t>
+          <t>-1428434.048330702</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>19156578.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -13833,7 +13833,7 @@
       </c>
       <c r="BM32" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BN32" t="inlineStr">
@@ -13853,7 +13853,7 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="BT32" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BU32" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="BV32" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="BW32" t="inlineStr">
@@ -13893,12 +13893,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -13918,12 +13918,12 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
@@ -13933,7 +13933,7 @@
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -13955,7 +13955,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -13965,42 +13965,42 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>492.79</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-3.87</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>510.601</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>39.1</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-4.13</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-9.39</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14075,17 +14075,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14096,66 +14096,66 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>2.87</v>
+        <v>1.25</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0.09</v>
+        <v>1.1</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>38.01000000000001</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>38.04</v>
+        <v>38</v>
       </c>
       <c r="AN33" t="n">
-        <v>39.97</v>
+        <v>39.92</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>41.20</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>-0.59</v>
+        <v>-0.47</v>
       </c>
       <c r="AR33" t="n">
-        <v>-0.88</v>
+        <v>-0.79</v>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14174,43 +14174,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>148636648.0239774</t>
+          <t>148451284.728169</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>73854919.59999999</v>
+        <v>69426442.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>55863021.8</t>
+          <t>52456837.4</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>33328621.84</v>
+        <v>33433682.52</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>17991897</t>
+          <t>16969605</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>4990346.878352229</t>
+          <t>4345764.102201018</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>3809528.634606227</t>
+          <t>800558.8333693519</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="BM33" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BN33" t="inlineStr">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14285,12 +14285,12 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BU33" t="inlineStr">
@@ -14300,7 +14300,7 @@
       </c>
       <c r="BV33" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="BW33" t="inlineStr">
@@ -14315,12 +14315,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14340,22 +14340,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14387,12 +14387,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>914.803</t>
+          <t>510.601</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14412,7 +14412,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14497,17 +14497,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14518,12 +14518,12 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -14533,51 +14533,51 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>4.35</v>
+        <v>2.87</v>
       </c>
       <c r="AI34" t="n">
-        <v>-1.59</v>
+        <v>-0.09</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>38.01000000000001</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>38.08</v>
+        <v>38.04</v>
       </c>
       <c r="AN34" t="n">
-        <v>40.03</v>
+        <v>39.97</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="AQ34" t="n">
-        <v>-0.75</v>
+        <v>-0.59</v>
       </c>
       <c r="AR34" t="n">
-        <v>-0.95</v>
+        <v>-0.88</v>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-135.29</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14596,43 +14596,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>148636648.0239774</t>
+          <t>148451284.728169</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>75499582.59999999</v>
+        <v>73854919.59999999</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>55792550.2</t>
+          <t>55863021.8</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>33454972.78</v>
+        <v>33328621.84</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>19707032</t>
+          <t>17991897</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>5205041.104487866</t>
+          <t>4990346.878352229</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>7886638.29228013</t>
+          <t>3809528.634606227</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="BM34" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BN34" t="inlineStr">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14712,7 +14712,7 @@
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="BV34" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="BW34" t="inlineStr">
@@ -14737,12 +14737,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -14762,17 +14762,17 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
